--- a/docs/design/ACSMS-SCR-022/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ファイルダウンロード画面_V1.2.xlsx
+++ b/docs/design/ACSMS-SCR-022/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ファイルダウンロード画面_V1.2.xlsx
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1632,16 +1632,126 @@
       <c r="AF4" s="10" t="n"/>
       <c r="AG4" s="11" t="n"/>
     </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="19" t="inlineStr">
+        <is>
+          <t>実装との差分是正（2026-07 の 2 件が本書へ未反映だった）：①日農DL許可チェック（`nichino_download_allowed_flg = false` → 403）の対象ロールに **CHUOKAI** を追加（従来は NICHINO_ADMIN / NICHINO_STAFF のみ）。②**自分が出力したファイルは本フラグを見ない**例外を追加（#52132）。本フラグは他組織へ見せてよいかを JA 側が決めるもので出力者本人を締め出す意図は無く、既定 FALSE のため例外が無いと自分の帳票をDLできなかった。突合は `t_file_download.created_by`（trim 済み文字列。空文字は本人扱いしない）。DL制限3ロール共通。③CHUOKAI の DataScope を「自JAのみ」→ **同一都道府県の全JA**（`fd.ja_id IS NULL OR j.todofuken_code = :user_todofuken_code`）へ拡大（#52132）。拡大先の県はセッションの `todofuken_code` で決まり他県は参照不可。セッションに当該項目が無い場合は自JAのみへフォールバック。一覧・個別DL・プレビュー・ZIP で同じ ja_id 集合を用い「一覧に出た行は個別DLでも通る」を不変条件とする</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="17" t="inlineStr"/>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="17" t="inlineStr"/>
+      <c r="AC5" s="10" t="n"/>
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="10" t="n"/>
+      <c r="AG5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/16</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>実装コード（`apps/backend/src/modules/file-download/`）との突合による是正：①**ACSMS-API-022-002（プレビュー）のレスポンス実体は `preview_url` + `file_name` の2項目のみ**。`file_download_id` / `file_size` / `content_type` / `expires_at` は `FilePreviewResponseDto` に存在せず、旧設計の残骸だった。処理手順もこれに合わせて修正（content_type 判定・expires_at 算出は行わない。有効期限はプロバイダ既定 TTL 3600 秒を暗黙適用）。②**ACSMS-API-022-004（ZIP一括DL）のファイル名規約を実装に合わせて修正**：`files_&lt;yyyyMMdd_HHmmss&gt;.zip` ではなく `一括ダウンロード_&lt;yyyyMMddHHmmss&gt;.zip`（`compactTimestampJst()`、区切りなし14桁）。ZIPも単体DLと同じ共通ヘルパー `sendBinaryAttachment` を経由するため `Content-Disposition` に `filename*=UTF-8''...` と `Content-Length` ヘッダが実際には付与される（旧記載は欠落していた）。③同エンドポイントのバリデーションエラー例のメッセージを実装の固定文言「入力値が不正です。詳細はerrorsフィールドを確認してください。」に修正（旧記載「入力値が正しくありません。」は他画面と不整合な誤記）。非配列入力時のメッセージ「ファイルIDの形式が不正です。」も追記。④同エンドポイントはレート制限 20回/分（`@Throttle(UPLOAD_DOWNLOAD_THROTTLE)`）を明示指定している旨を概要表・例外処理に追記（API-022-001〜003 はグローバル既定のみ）。⑤`target_month` の DB 制約表記を「NOT NULL DEFAULT ''」→ 実際の「nullable・DEFAULT ''」に修正（`database-design.md` §t_file_download と不整合だった）。⑥API-022-003 の `Content-Type` 判定ロジック参照先を「API-022-002と同じ」から共通ユーティリティ `contentTypeFor` に修正（②の是正により002は content_type を扱わなくなったため）。⑦一括DL監査ログ `after_value` の実フィールド名（`bulk`, `zip_file_name`, `file_count`, `file_download_ids`）を明記</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="17" t="inlineStr"/>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="17" t="inlineStr"/>
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="42">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="C5:G5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
@@ -1649,19 +1759,25 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1834,7 +1950,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2305,7 +2421,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3120,7 +3236,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3322,7 +3438,7 @@
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="19" t="inlineStr">
         <is>
-          <t>指定したファイルのプレビュー用署名付き URL（S3 short-lived presigned URL）+ メタ情報を取得する。FE 側でモーダルにて表示する。データソースは `t_file_download`。DataScope チェックに加え、日農（NICHINO_ADMIN / NICHINO_STAFF）が `nichino_download_allowed_flg=false` のファイルをプレビューしようとした場合は HTTP 403 を返却する。</t>
+          <t>指定したファイルのプレビュー用署名付き URL（S3 short-lived presigned URL）+ ファイル名を取得する。FE 側でモーダルにて表示する。データソースは `t_file_download`。DataScope チェックに加え、日農（NICHINO_ADMIN / NICHINO_STAFF）が `nichino_download_allowed_flg=false` のファイルをプレビューしようとした場合は HTTP 403 を返却する。</t>
         </is>
       </c>
       <c r="T7" s="10" t="n"/>
@@ -3681,7 +3797,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5521,7 +5637,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>対象年月（DB カラムは NOT NULL DEFAULT '' のため未設定時は空文字。レスポンス型は nullable string）</t>
+          <t>対象年月（DB カラムは nullable・DEFAULT ''。月次でない出力は NULL、未設定時は空文字のケースもある）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -6640,10 +6756,10 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1">
+    <row r="95" ht="108" customHeight="1">
       <c r="D95" s="41" t="inlineStr">
         <is>
-          <t>`CHUOKAI`: 自中央会 + 管轄 JA のファイル + 全 JA 向けファイル（`fd.ja_id IN (:managed_ja_ids) OR fd.ja_id IS NULL`）</t>
+          <t>`CHUOKAI`: **同一都道府県の全 JA** のファイル + 全 JA 向けファイル（`fd.ja_id IS NULL OR j.todofuken_code = :user_todofuken_code`。`m_ja` は既に LEFT JOIN 済みのため追加 JOIN は不要）。判定は `role_code = CHUOKAI` で限定する — `todofuken_code` の有無だけで分岐すると JA_HONTEN / JA_KANRI_SHITEN も県内全 JA へ広がってしまうため（顧客要件 2026-07 / #52132。従来は自 JA のみ）</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7533,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7541,7 +7657,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>指定したファイルのプレビュー用署名付き URL（S3 short-lived presigned URL）+ メタ情報を取得する。FE 側でモーダルにて表示する。データソースは `t_file_download`。DataScope チェックに加え、日農（NICHINO_ADMIN / NICHINO_STAFF）が `nichino_download_allowed_flg=false` のファイルをプレビューしようとした場合は HTTP 403 を返却する。</t>
+          <t>指定したファイルのプレビュー用署名付き URL（S3 short-lived presigned URL）+ ファイル名を取得する。FE 側でモーダルにて表示する。データソースは `t_file_download`。DataScope チェックに加え、日農（NICHINO_ADMIN / NICHINO_STAFF）が `nichino_download_allowed_flg=false` のファイルをプレビューしようとした場合は HTTP 403 を返却する。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -8282,14 +8398,14 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="72" customHeight="1">
       <c r="B29" s="31" t="n">
         <v>2</v>
       </c>
       <c r="C29" s="37" t="n"/>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>file_download_id</t>
+          <t>preview_url</t>
         </is>
       </c>
       <c r="E29" s="10" t="n"/>
@@ -8302,7 +8418,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N29" s="10" t="n"/>
@@ -8329,7 +8445,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>ファイルダウンロード ID</t>
+          <t>プレビュー用署名付き URL（S3 presigned URL。有効期限は Storage プロバイダの既定 TTL 3600 秒＝1 時間。呼び出し側で expiresIn を上書きしていない）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -8342,7 +8458,7 @@
       <c r="B30" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="38" t="n"/>
+      <c r="C30" s="39" t="n"/>
       <c r="D30" s="19" t="inlineStr">
         <is>
           <t>file_name</t>
@@ -8394,132 +8510,21 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>file_size</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="17" t="inlineStr"/>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U31" s="10" t="n"/>
-      <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Z31" s="10" t="n"/>
-      <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
-      <c r="AC31" s="10" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="19" t="inlineStr">
-        <is>
-          <t>ファイルサイズ（バイト）</t>
-        </is>
-      </c>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="10" t="n"/>
-      <c r="AI31" s="10" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
-      <c r="AK31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="B32" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>content_type</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="17" t="inlineStr"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="inlineStr"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="19" t="inlineStr">
-        <is>
-          <t>コンテンツ MIME タイプ（例: `application/pdf`, `text/csv`）</t>
-        </is>
-      </c>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="B33" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" s="38" t="n"/>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>preview_url</t>
-        </is>
-      </c>
+    <row r="31" ht="19.5" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/file-download/101/preview</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -8527,216 +8532,95 @@
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
+      <c r="L33" s="10" t="n"/>
+      <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="17" t="inlineStr"/>
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n"/>
       <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
       <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="17" t="inlineStr"/>
+      <c r="X33" s="10" t="n"/>
+      <c r="Y33" s="10" t="n"/>
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="10" t="n"/>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="19" t="inlineStr">
-        <is>
-          <t>プレビュー用署名付き URL（S3 presigned URL、有効期限 1 時間）</t>
-        </is>
-      </c>
+      <c r="AE33" s="10" t="n"/>
+      <c r="AF33" s="10" t="n"/>
       <c r="AG33" s="10" t="n"/>
       <c r="AH33" s="10" t="n"/>
       <c r="AI33" s="10" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="C34" s="39" t="n"/>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>expires_at</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr"/>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD HH:mm:ss</t>
-        </is>
-      </c>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr"/>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr">
-        <is>
-          <t>署名付き URL の有効期限（ISO 8601 形式）</t>
-        </is>
-      </c>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="19.5" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="B36" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/file-download/101/preview</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
-      <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
-      <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="B39" s="40" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="180" customHeight="1">
-      <c r="C40" s="19" t="inlineStr">
+    <row r="36" ht="108" customHeight="1">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
-    "file_download_id": 101,
-    "file_name": "zougen_tsuchi_202604.pdf",
-    "file_size": 524288,
-    "content_type": "application/pdf",
     "preview_url": "https://s3.ap-northeast-1.amazonaws.com/agrinews-prod-files/ja-1/zougen_tsuchi_202604.pdf?X-Amz-Algorithm=AWS4-HMAC-SHA256&amp;X-Amz-Expires=3600&amp;...",
-    "expires_at": "2026-05-07T11:30:00+09:00"
+    "file_name": "zougen_tsuchi_202604.pdf"
   }
 }</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="11" t="n"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="B42" s="40" t="inlineStr">
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="10" t="n"/>
+      <c r="Z36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n"/>
+      <c r="AB36" s="10" t="n"/>
+      <c r="AC36" s="10" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="10" t="n"/>
+      <c r="AF36" s="10" t="n"/>
+      <c r="AG36" s="10" t="n"/>
+      <c r="AH36" s="10" t="n"/>
+      <c r="AI36" s="10" t="n"/>
+      <c r="AJ36" s="10" t="n"/>
+      <c r="AK36" s="11" t="n"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 401 — UNAUTHORIZED）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="C43" s="19" t="inlineStr">
+    <row r="39" ht="72" customHeight="1">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -8744,50 +8628,50 @@
 }</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="10" t="n"/>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="10" t="n"/>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
-      <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="10" t="n"/>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="10" t="n"/>
-      <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
-      <c r="AK43" s="11" t="n"/>
-    </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="B45" s="40" t="inlineStr">
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="10" t="n"/>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="10" t="n"/>
+      <c r="AC39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="10" t="n"/>
+      <c r="AF39" s="10" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 403 — FORBIDDEN）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="C46" s="19" t="inlineStr">
+    <row r="42" ht="72" customHeight="1">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -8795,50 +8679,50 @@
 }</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="11" t="n"/>
-    </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="B48" s="40" t="inlineStr">
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="10" t="n"/>
+      <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="10" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="10" t="n"/>
+      <c r="AF42" s="10" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="11" t="n"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 404 — NOT_FOUND）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="72" customHeight="1">
-      <c r="C49" s="19" t="inlineStr">
+    <row r="45" ht="72" customHeight="1">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -8846,50 +8730,50 @@
 }</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="10" t="n"/>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="n"/>
-      <c r="Y49" s="10" t="n"/>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="10" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
-      <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="10" t="n"/>
-      <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="B51" s="40" t="inlineStr">
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="n"/>
+      <c r="Y45" s="10" t="n"/>
+      <c r="Z45" s="10" t="n"/>
+      <c r="AA45" s="10" t="n"/>
+      <c r="AB45" s="10" t="n"/>
+      <c r="AC45" s="10" t="n"/>
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="10" t="n"/>
+      <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="10" t="n"/>
+      <c r="AH45" s="10" t="n"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
+      <c r="AK45" s="11" t="n"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 500 — INTERNAL_SERVER_ERROR）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="72" customHeight="1">
-      <c r="C52" s="19" t="inlineStr">
+    <row r="48" ht="72" customHeight="1">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -8897,201 +8781,223 @@
 }</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="10" t="n"/>
-      <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
-      <c r="R52" s="10" t="n"/>
-      <c r="S52" s="10" t="n"/>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="10" t="n"/>
-      <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AA52" s="10" t="n"/>
-      <c r="AB52" s="10" t="n"/>
-      <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
-      <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1"/>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="27" t="inlineStr">
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="10" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="10" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="10" t="n"/>
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="10" t="n"/>
+      <c r="AF48" s="10" t="n"/>
+      <c r="AG48" s="10" t="n"/>
+      <c r="AH48" s="10" t="n"/>
+      <c r="AI48" s="10" t="n"/>
+      <c r="AJ48" s="10" t="n"/>
+      <c r="AK48" s="11" t="n"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1"/>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>`file_download_id`: 必須、整数、最小 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="C57" s="41" t="inlineStr">
         <is>
-          <t>`file_download_id`: 必須、整数、最小 1。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+          <t>必要権限: `file.download`</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: NICHINO_ADMIN / NICHINO_STAFF / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN（全 5 ロール）</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="C59" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="72" customHeight="1">
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>DataScope: API-022-001 と同一（`ja_id IS NULL` の全 JA 向けファイルは全ロール参照可）。レコードの `ja_id` がユーザのスコープ外の場合は HTTP 404 (`NOT_FOUND`) を返却（存在隠蔽 — security.md `assertJaScope` 規則）。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="C61" s="41" t="inlineStr">
-        <is>
-          <t>必要権限: `file.download`</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="C62" s="41" t="inlineStr">
-        <is>
-          <t>該当権限保持ロール: NICHINO_ADMIN / NICHINO_STAFF / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN（全 5 ロール）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="72" customHeight="1">
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>DataScope: API-022-001 と同一（`ja_id IS NULL` の全 JA 向けファイルは全ロール参照可）。レコードの `ja_id` がユーザのスコープ外の場合は HTTP 404 (`NOT_FOUND`) を返却（存在隠蔽 — security.md `assertJaScope` 規則）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="B65" s="27" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="180" customHeight="1">
-      <c r="C66" s="42" t="inlineStr">
-        <is>
-          <t>SELECT
-    fd.file_download_id,
-    fd.ja_id,
-    fd.file_name,
-    fd.file_path,
-    fd.file_size,
-    fd.nichino_download_allowed_flg
+    <row r="62" ht="72" customHeight="1">
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>SELECT *
   FROM t_file_download fd
  WHERE fd.file_download_id = :file_download_id
    AND fd.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
-      <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="10" t="n"/>
-      <c r="M66" s="10" t="n"/>
-      <c r="N66" s="10" t="n"/>
-      <c r="O66" s="10" t="n"/>
-      <c r="P66" s="10" t="n"/>
-      <c r="Q66" s="10" t="n"/>
-      <c r="R66" s="10" t="n"/>
-      <c r="S66" s="10" t="n"/>
-      <c r="T66" s="10" t="n"/>
-      <c r="U66" s="10" t="n"/>
-      <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n"/>
-      <c r="X66" s="10" t="n"/>
-      <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="10" t="n"/>
-      <c r="AA66" s="10" t="n"/>
-      <c r="AB66" s="10" t="n"/>
-      <c r="AC66" s="10" t="n"/>
-      <c r="AD66" s="10" t="n"/>
-      <c r="AE66" s="10" t="n"/>
-      <c r="AF66" s="10" t="n"/>
-      <c r="AG66" s="10" t="n"/>
-      <c r="AH66" s="10" t="n"/>
-      <c r="AI66" s="10" t="n"/>
-      <c r="AJ66" s="10" t="n"/>
-      <c r="AK66" s="11" t="n"/>
-    </row>
-    <row r="67" ht="18" customHeight="1">
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="10" t="n"/>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="10" t="n"/>
+      <c r="AF62" s="10" t="n"/>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>DataScope に違反する場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>4.4 日農ダウンロード許可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザが**DL制限ロール**（NICHINO_ADMIN / NICHINO_STAFF / **CHUOKAI**）で、かつ対象レコードの `nichino_download_allowed_flg = false` の場合、HTTP 403 (`FORBIDDEN`) を返却する（メッセージ: `このファイルは日農のダウンロードが許可されていません。`）。中央会が対象に加わったのは顧客要件 2026-07 による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="72" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="C68" s="41" t="inlineStr">
-        <is>
-          <t>DataScope に違反する場合：HTTP 404 (`NOT_FOUND`)（存在隠蔽）</t>
+          <t>**例外：自分が出力したファイルは本フラグを見ない**（顧客要件 2026-07 / #52132）。本フラグは「他組織（日農・中央会）へ自組織のファイルを見せてよいか」を JA 側が決めるものであり、出力した本人まで締め出す意図は無い。既定値が FALSE のため、この例外が無いと中央会が自分で出力した帳票をその場でダウンロードできなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="72" customHeight="1">
+      <c r="D68" s="41" t="inlineStr">
+        <is>
+          <t>本人判定は `t_file_download.created_by`（`m_account.account_id` を varchar で保持。一覧 SQL の `m_account.account_id::text = fd.created_by` と同じ前提）で行い、両辺を trim 済み文字列に揃えて突合する。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>4.4 日農ダウンロード許可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザが日農（NICHINO_ADMIN / NICHINO_STAFF）で、かつ対象レコードの `nichino_download_allowed_flg = false` の場合、HTTP 403 (`FORBIDDEN`) を返却する（メッセージ: `このファイルは日農のダウンロードが許可されていません。`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>`created_by` が空文字の行は**本人扱いしない**（安全側に倒す）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>例外は DL制限3ロール共通。日農にも同じ穴があるため中央会だけの特例にはしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="54" customHeight="1">
       <c r="C71" s="41" t="inlineStr">
         <is>
-          <t>行は一覧に表示されるため、存在を隠す 404 ではなく 403 を返す（`assertNichinoDownloadAllowed` 規則）。JA 系ロールは本フラグの影響を受けない。</t>
+          <t>行は一覧に表示されるため、存在を隠す 404 ではなく 403 を返す（`assertNichinoDownloadAllowed` 規則）。JA_HONTEN / JA_KANRI_SHITEN は本フラグの影響を受けない。</t>
         </is>
       </c>
     </row>
@@ -9102,24 +9008,24 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="72" customHeight="1">
+    <row r="73" ht="36" customHeight="1">
       <c r="C73" s="41" t="inlineStr">
         <is>
-          <t>ファイル拡張子から `content_type` を判定（`.pdf` → `application/pdf`, `.csv` → `text/csv`, `.xlsx` → `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="36" customHeight="1">
+          <t>`content_type` の判定・付与は行わない（このエンドポイントのレスポンスに `content_type` フィールドは存在しない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="72" customHeight="1">
       <c r="C74" s="41" t="inlineStr">
         <is>
-          <t>AWS S3 SDK で `file_path` に対する presigned URL を発行（有効期限 3600 秒 / 1 時間）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
+          <t>Storage サービス（S3 / MinIO）の `getSignedUrl(file_path)` で presigned URL を発行。`expiresIn` は明示的に指定せず、プロバイダ既定 TTL（`DEFAULT_SIGNED_URL_TTL_SECONDS` = 3600 秒 / 1 時間）を使用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="54" customHeight="1">
       <c r="C75" s="41" t="inlineStr">
         <is>
-          <t>レスポンスに `preview_url` + `expires_at` を含めて返却。</t>
+          <t>レスポンスは `preview_url` + `file_name` の 2 項目のみ（`expires_at` は返さない — 有効期限を確認したい場合は署名付き URL のクエリパラメータ `X-Amz-Expires` を参照する）。</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9079,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="145">
+  <mergeCells count="125">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
@@ -9181,91 +9087,72 @@
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C66:AK66"/>
-    <mergeCell ref="T33:X33"/>
+    <mergeCell ref="C29:C30"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="C53:AK53"/>
     <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C68:AK68"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="C45:AK45"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="D33:L33"/>
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="B65:AK65"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="T31:X31"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="D34:L34"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="C48:AK48"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B47:I47"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="C49:AK49"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C33:AK33"/>
+    <mergeCell ref="B61:AK61"/>
     <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="C42:AK42"/>
     <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="B69:AK69"/>
-    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="D29:L29"/>
-    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="A25:AK25"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="C39:AK39"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="C37:AK37"/>
-    <mergeCell ref="A55:AK55"/>
-    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="B52:AK52"/>
     <mergeCell ref="C78:AK78"/>
-    <mergeCell ref="T32:X32"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C62:AK62"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="C82:AK82"/>
@@ -9275,36 +9162,36 @@
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="M34:P34"/>
     <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="C63:AK63"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="A51:AK51"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="C43:AK43"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="C36:AK36"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="B54:AK54"/>
     <mergeCell ref="B72:AK72"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B56:AK56"/>
-    <mergeCell ref="D32:L32"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="Y32:AE32"/>
-    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="D68:AK68"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="C40:AK40"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
@@ -9315,8 +9202,7 @@
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="D31:L31"/>
-    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
@@ -9330,7 +9216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK96"/>
+  <dimension ref="A1:AK100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9491,7 +9377,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10852,17 +10738,10 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="198" customHeight="1">
+    <row r="63" ht="72" customHeight="1">
       <c r="C63" s="42" t="inlineStr">
         <is>
-          <t>SELECT
-    fd.file_download_id,
-    fd.ja_id,
-    fd.file_name,
-    fd.file_path,
-    fd.file_size,
-    fd.record_count,
-    fd.nichino_download_allowed_flg
+          <t>SELECT *
   FROM t_file_download fd
  WHERE fd.file_download_id = :file_download_id
    AND fd.deleted_at IS NULL</t>
@@ -10924,92 +10803,120 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="72" customHeight="1">
+    <row r="67" ht="90" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザが日農（NICHINO_ADMIN / NICHINO_STAFF）で、かつ対象レコードの `nichino_download_allowed_flg = false` の場合、HTTP 403 (`FORBIDDEN`) を返却する（メッセージ: `このファイルは日農のダウンロードが許可されていません。`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+          <t>ログインユーザが**DL制限ロール**（NICHINO_ADMIN / NICHINO_STAFF / **CHUOKAI**）で、かつ対象レコードの `nichino_download_allowed_flg = false` の場合、HTTP 403 (`FORBIDDEN`) を返却する（メッセージ: `このファイルは日農のダウンロードが許可されていません。`）。中央会が対象に加わったのは顧客要件 2026-07 による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="72" customHeight="1">
       <c r="C68" s="41" t="inlineStr">
         <is>
-          <t>行は一覧に表示されるため、存在を隠す 404 ではなく 403 を返す（`assertNichinoDownloadAllowed` 規則）。JA 系ロールは本フラグの影響を受けない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="B69" s="27" t="inlineStr">
+          <t>**例外：自分が出力したファイルは本フラグを見ない**（顧客要件 2026-07 / #52132）。本フラグは「他組織（日農・中央会）へ自組織のファイルを見せてよいか」を JA 側が決めるものであり、出力した本人まで締め出す意図は無い。既定値が FALSE のため、この例外が無いと中央会が自分で出力した帳票をその場でダウンロードできなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="72" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>本人判定は `t_file_download.created_by`（`m_account.account_id` を varchar で保持。一覧 SQL の `m_account.account_id::text = fd.created_by` と同じ前提）で行い、両辺を trim 済み文字列に揃えて突合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>`created_by` が空文字の行は**本人扱いしない**（安全側に倒す）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>例外は DL制限3ロール共通。日農にも同じ穴があるため中央会だけの特例にはしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="54" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>行は一覧に表示されるため、存在を隠す 404 ではなく 403 を返す（`assertNichinoDownloadAllowed` 規則）。JA_HONTEN / JA_KANRI_SHITEN は本フラグの影響を受けない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>4.5 ファイル取得</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
+    <row r="74" ht="36" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>AWS S3 SDK で `file_path` のオブジェクトを取得し、レスポンスストリームへパイプ。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>ストレージ取得はトランザクション外で先に行う（失敗時に `t_log` を残さないため）。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>レスポンスヘッダ:</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="D73" s="41" t="inlineStr">
-        <is>
-          <t>`Content-Type`: ファイル拡張子から判定（API-022-002 と同じロジック）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="54" customHeight="1">
-      <c r="D74" s="41" t="inlineStr">
+    <row r="77" ht="72" customHeight="1">
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>`Content-Type`: ファイル拡張子から判定（共通ユーティリティ `contentTypeFor`。API-022-002 のプレビューはレスポンスに `content_type` を含まないため対象外 — ACSMS-SCR-023 アップロード画面のダウンロード系エンドポイントとも共有するロジック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="54" customHeight="1">
+      <c r="D78" s="41" t="inlineStr">
         <is>
           <t>`Content-Disposition`: `attachment; filename="&lt;file_name&gt;"; filename*=UTF-8''&lt;URL-encoded file_name&gt;`</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>`Content-Length`: `fd.file_size`</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>`Content-Length`: `fd.file_size`（DB 値が NULL の場合のみ取得したバイナリの実サイズにフォールバック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="D80" s="41" t="inlineStr">
         <is>
           <t>`Cache-Control`: `no-store`</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録（`t_log`）</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="36" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
+    <row r="82" ht="36" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>ダウンロード実行の証跡は `t_log`（log_type=4 / operation=DOWNLOAD）のみ。`t_file_download`</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="180" customHeight="1">
-      <c r="C79" s="42" t="inlineStr">
+    <row r="83" ht="180" customHeight="1">
+      <c r="C83" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -11023,155 +10930,155 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="10" t="n"/>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
-      <c r="T79" s="10" t="n"/>
-      <c r="U79" s="10" t="n"/>
-      <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
-      <c r="X79" s="10" t="n"/>
-      <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
-      <c r="AA79" s="10" t="n"/>
-      <c r="AB79" s="10" t="n"/>
-      <c r="AC79" s="10" t="n"/>
-      <c r="AD79" s="10" t="n"/>
-      <c r="AE79" s="10" t="n"/>
-      <c r="AF79" s="10" t="n"/>
-      <c r="AG79" s="10" t="n"/>
-      <c r="AH79" s="10" t="n"/>
-      <c r="AI79" s="10" t="n"/>
-      <c r="AJ79" s="10" t="n"/>
-      <c r="AK79" s="11" t="n"/>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>`log_type = 4`（ファイル操作）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>`operation = 'DOWNLOAD'`（ダウンロード操作）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>`before_value`: 空文字（取得時の状態変化はないため）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>`after_value`: ダウンロードしたファイルのメタ情報 JSON（`file_download_id`, `file_name`, `file_size`, `ja_id`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="C85" s="41" t="inlineStr">
         <is>
-          <t>バイナリストリームをクライアントへ送信。</t>
+          <t>`operation = 'DOWNLOAD'`（ダウンロード操作）。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>上記ヘッダを設定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
+          <t>`before_value`: 空文字（取得時の状態変化はないため）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
       <c r="C87" s="41" t="inlineStr">
         <is>
-          <t>ステータス 200。</t>
+          <t>`after_value`: ダウンロードしたファイルのメタ情報 JSON（`file_download_id`, `file_name`, `file_size`, `ja_id`）。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>4.8 例外処理</t>
+          <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>バイナリストリームをクライアントへ送信。</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="36" customHeight="1">
+          <t>上記ヘッダを設定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>日農が `nichino_download_allowed_flg=false` のファイルをダウンロードしようとした場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない、または DataScope 違反の場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
+          <t>ステータス 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>4.8 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
       <c r="C93" s="41" t="inlineStr">
         <is>
-          <t>S3 / DB 接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="C94" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
+        <is>
+          <t>日農が `nichino_download_allowed_flg=false` のファイルをダウンロードしようとした場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない、または DataScope 違反の場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>S3 / DB 接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
+        <is>
           <t>レート制限超過の場合：HTTP 429 (`TOO_MANY_REQUESTS`)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>エラーログ記録（トランザクション外で別途記録）:</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="162" customHeight="1">
-      <c r="C96" s="42" t="inlineStr">
+    <row r="100" ht="162" customHeight="1">
+      <c r="C100" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -11184,50 +11091,52 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="10" t="n"/>
-      <c r="F96" s="10" t="n"/>
-      <c r="G96" s="10" t="n"/>
-      <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="10" t="n"/>
-      <c r="M96" s="10" t="n"/>
-      <c r="N96" s="10" t="n"/>
-      <c r="O96" s="10" t="n"/>
-      <c r="P96" s="10" t="n"/>
-      <c r="Q96" s="10" t="n"/>
-      <c r="R96" s="10" t="n"/>
-      <c r="S96" s="10" t="n"/>
-      <c r="T96" s="10" t="n"/>
-      <c r="U96" s="10" t="n"/>
-      <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
-      <c r="X96" s="10" t="n"/>
-      <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="10" t="n"/>
-      <c r="AA96" s="10" t="n"/>
-      <c r="AB96" s="10" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="10" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="10" t="n"/>
-      <c r="AK96" s="11" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="10" t="n"/>
+      <c r="AK100" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="143">
+  <mergeCells count="147">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="C57:AK57"/>
+    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="D71:AK71"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="C34:AK34"/>
     <mergeCell ref="N18:AK18"/>
@@ -11241,17 +11150,19 @@
     <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D73:AK73"/>
+    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
@@ -11260,28 +11171,28 @@
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="C95:AK95"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="D77:AK77"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="D75:AK75"/>
     <mergeCell ref="B66:AK66"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="C49:AK49"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="B39:I39"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="A52:AK52"/>
-    <mergeCell ref="B69:AK69"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="B55:AK55"/>
     <mergeCell ref="J13:AK13"/>
@@ -11294,20 +11205,19 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
     <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="D76:AK76"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="C72:AK72"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="C37:AK37"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
@@ -11317,16 +11227,16 @@
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="C54:AK54"/>
     <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="C93:AK93"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="C56:AK56"/>
+    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="C43:AK43"/>
@@ -11341,12 +11251,12 @@
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="C83:AK83"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="D74:AK74"/>
     <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="C40:AK40"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
@@ -11356,11 +11266,12 @@
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="B62:AK62"/>
+    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
@@ -11375,7 +11286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK83"/>
+  <dimension ref="A1:AK87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -11536,7 +11447,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12425,7 +12336,7 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="126" customHeight="1">
       <c r="B30" s="31" t="inlineStr"/>
       <c r="C30" s="19" t="inlineStr"/>
       <c r="D30" s="10" t="n"/>
@@ -12458,7 +12369,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>`attachment; filename="files_&lt;yyyyMMdd_HHmmss&gt;.zip"`</t>
+          <t>`attachment; filename="&lt;ASCIIフォールバック名&gt;"; filename*=UTF-8''&lt;URLエンコードしたファイル名&gt;`。ファイル名は `一括ダウンロード_&lt;yyyyMMddHHmmss&gt;.zip`（日本語プレフィックス＋日時14桁、区切りのアンダースコアは日時の前に1つのみ）。ASCIIフォールバック名は非ASCII文字（日本語部分）を `_` に置換したもの。</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -12500,7 +12411,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>`no-store`</t>
+          <t>ZIP ファイルサイズ（バイト）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -12509,16 +12420,58 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="B33" s="40" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="inlineStr"/>
+      <c r="C32" s="19" t="inlineStr"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>`no-store`</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="72" customHeight="1">
-      <c r="C34" s="19" t="inlineStr">
+    <row r="35" ht="72" customHeight="1">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/file-download/download-zip
 {
@@ -12526,156 +12479,157 @@
 }</t>
         </is>
       </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="10" t="n"/>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="10" t="n"/>
-      <c r="Q34" s="10" t="n"/>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="10" t="n"/>
-      <c r="T34" s="10" t="n"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="10" t="n"/>
-      <c r="Y34" s="10" t="n"/>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="10" t="n"/>
-      <c r="AF34" s="10" t="n"/>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="B36" s="40" t="inlineStr">
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="10" t="n"/>
+      <c r="AF35" s="10" t="n"/>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="108" customHeight="1">
-      <c r="C37" s="19" t="inlineStr">
+    <row r="38" ht="126" customHeight="1">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>HTTP/1.1 200 OK
 Content-Type: application/zip
-Content-Disposition: attachment; filename="files_20260702_101530.zip"
+Content-Disposition: attachment; filename="_________20260702101530.zip"; filename*=UTF-8''%E4%B8%80%E6%8B%AC%E3%83%80%E3%82%A6%E3%83%B3%E3%83%AD%E3%83%BC%E3%83%89_20260702101530.zip
+Content-Length: 1048576
 Cache-Control: no-store
 &lt;binary ZIP stream&gt;</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
-      <c r="T37" s="10" t="n"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
-      <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1">
-      <c r="B39" s="40" t="inlineStr">
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 400 — VALIDATION_ERROR）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="126" customHeight="1">
-      <c r="C40" s="19" t="inlineStr">
+    <row r="41" ht="126" customHeight="1">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
-  "message": "入力値が正しくありません。",
+  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
   "errors": [
     { "field": "file_download_ids", "message": "ファイルを選択してください。" }
   ]
 }</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="11" t="n"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1">
-      <c r="B42" s="40" t="inlineStr">
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="10" t="n"/>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="10" t="n"/>
+      <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 401 — UNAUTHORIZED）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="C43" s="19" t="inlineStr">
+    <row r="44" ht="72" customHeight="1">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -12683,50 +12637,50 @@
 }</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="10" t="n"/>
-      <c r="T43" s="10" t="n"/>
-      <c r="U43" s="10" t="n"/>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
-      <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="10" t="n"/>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="10" t="n"/>
-      <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
-      <c r="AK43" s="11" t="n"/>
-    </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="B45" s="40" t="inlineStr">
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="10" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 403 — FORBIDDEN）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="C46" s="19" t="inlineStr">
+    <row r="47" ht="72" customHeight="1">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -12734,50 +12688,50 @@
 }</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="11" t="n"/>
-    </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="B48" s="40" t="inlineStr">
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="10" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="10" t="n"/>
+      <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 404 — NOT_FOUND）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="72" customHeight="1">
-      <c r="C49" s="19" t="inlineStr">
+    <row r="50" ht="72" customHeight="1">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -12785,50 +12739,50 @@
 }</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="10" t="n"/>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="n"/>
-      <c r="Y49" s="10" t="n"/>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="10" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
-      <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="10" t="n"/>
-      <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="B51" s="40" t="inlineStr">
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 HTTP 500 — INTERNAL_SERVER_ERROR）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="72" customHeight="1">
-      <c r="C52" s="19" t="inlineStr">
+    <row r="53" ht="72" customHeight="1">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -12836,370 +12790,400 @@
 }</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="10" t="n"/>
-      <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
-      <c r="R52" s="10" t="n"/>
-      <c r="S52" s="10" t="n"/>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="10" t="n"/>
-      <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AA52" s="10" t="n"/>
-      <c r="AB52" s="10" t="n"/>
-      <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
-      <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1"/>
-    <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="27" t="inlineStr">
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="10" t="n"/>
+      <c r="AF53" s="10" t="n"/>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="27" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>`file_download_ids`: 必須、配列、1〜50 件、要素は整数、重複不可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="D58" s="41" t="inlineStr">
-        <is>
-          <t>空配列: `ファイルを選択してください。`</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="D59" s="41" t="inlineStr">
         <is>
-          <t>51 件以上: `一括ダウンロードは最大50件までです。`</t>
+          <t>配列でない値: `ファイルIDの形式が不正です。`</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>重複: `ファイルIDが重複しています。`</t>
+          <t>空配列: `ファイルを選択してください。`</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="D61" s="41" t="inlineStr">
         <is>
+          <t>51 件以上: `一括ダウンロードは最大50件までです。`</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>重複: `ファイルIDが重複しています。`</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="D63" s="41" t="inlineStr">
+        <is>
           <t>非整数: `ファイルIDは整数で指定してください。`</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。未認証: HTTP 401。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="C64" s="41" t="inlineStr">
+    <row r="66" ht="18" customHeight="1">
+      <c r="C66" s="41" t="inlineStr">
         <is>
           <t>必要権限: `file.download`。権限不足: HTTP 403。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="B65" s="27" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得・各ファイルのチェック</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="36" customHeight="1">
-      <c r="C66" s="41" t="inlineStr">
+    <row r="68" ht="36" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
         <is>
           <t>`file_download_ids` の各 ID について `t_file_download`（`deleted_at IS NULL`）を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>各行に対し以下を実施する:</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="36" customHeight="1">
-      <c r="D68" s="41" t="inlineStr">
+    <row r="70" ht="36" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
         <is>
           <t>DataScope チェック（API-022-001 と同一）。スコープ外は HTTP 404（存在隠蔽）。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="36" customHeight="1">
-      <c r="D69" s="41" t="inlineStr">
+    <row r="71" ht="36" customHeight="1">
+      <c r="D71" s="41" t="inlineStr">
         <is>
           <t>日農ダウンロード許可チェック（API-022-003 4.4 と同一）。日農かつ `nichino_download_allowed_flg=false` は HTTP 403。</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>4.4 ZIP 生成・返却</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
-        <is>
-          <t>各ファイルを S3 から取得し、1 つの ZIP アーカイブに追加してストリーム返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="54" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>レスポンスヘッダ: `Content-Type: application/zip`, `Content-Disposition: attachment; filename="files_&lt;yyyyMMdd_HHmmss&gt;.zip"`, `Cache-Control: no-store`。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録（`t_log`）</t>
+    <row r="73" ht="36" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>各ファイルを S3 から並列取得し、`buildZipArchive` で 1 つの ZIP アーカイブへまとめてストリーム返却する。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="C74" s="41" t="inlineStr">
         <is>
-          <t>バッチ全体で `t_log`（log_type=4 / operation=DOWNLOAD）を **1 件のみ** 記録する。`t_file_download` への INSERT は行わない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
+          <t>ZIP ファイル名は `一括ダウンロード_&lt;yyyyMMddHHmmss&gt;`（JST、`compactTimestampJst()` — 区切りなしの日時14桁）+ `.zip`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1">
       <c r="C75" s="41" t="inlineStr">
         <is>
-          <t>`after_value`: 一括ダウンロードしたファイルのメタ情報 JSON（対象 `file_download_id` 配列・件数）。</t>
+          <t>レスポンスは API-022-003 と同じ共通ヘルパー `sendBinaryAttachment` で送出するため、`Content-Type: application/zip`, `Content-Length`, `Cache-Control: no-store` に加えて `Content-Disposition: attachment; filename="&lt;ASCIIフォールバック名&gt;"; filename*=UTF-8''&lt;URLエンコードしたファイル名&gt;` を設定する。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="27" t="inlineStr">
         <is>
+          <t>4.5 操作ログ記録（`t_log`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
+        <is>
+          <t>バッチ全体で `t_log`（log_type=4 / operation=DOWNLOAD）を **1 件のみ** 記録する。`t_file_download` への INSERT は行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="54" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>`after_value`: 一括ダウンロードしたファイルのメタ情報 JSON（`bulk: true`, `zip_file_name`, `file_count`, `file_download_ids` 配列。`target_id` はバッチ全体を指すため NULL）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
+        <is>
           <t>4.6 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>認証失敗: HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>権限がない: HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>日農が `nichino_download_allowed_flg=false` のファイルを含めて要求した場合: HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>いずれかのファイルが存在しない、または DataScope 違反: HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="C81" s="41" t="inlineStr">
         <is>
+          <t>権限がない: HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>日農が `nichino_download_allowed_flg=false` のファイルを含めて要求した場合: HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>いずれかのファイルが存在しない、または DataScope 違反: HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
+        <is>
           <t>バリデーションエラー: HTTP 400 (`VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>S3 / DB 接続エラー等: HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
+    <row r="86" ht="36" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>レート制限超過（20 回 / 分）の場合: HTTP 429 (`TOO_MANY_REQUESTS`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>エラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="125">
+  <mergeCells count="134">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C53:AK53"/>
+    <mergeCell ref="D71:AK71"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="C34:AK34"/>
+    <mergeCell ref="M32:P32"/>
     <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="D58:AK58"/>
+    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C44:AK44"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="C75:AK75"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="B65:AK65"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
-    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B45:I45"/>
     <mergeCell ref="D61:AK61"/>
+    <mergeCell ref="C38:AK38"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="C49:AK49"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="B67:AK67"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B39:I39"/>
     <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="Y30:AE30"/>
+    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
+    <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="B33:I33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
     <mergeCell ref="Y28:AE28"/>
-    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="C37:AK37"/>
-    <mergeCell ref="A55:AK55"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="B57:AK57"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="C41:AK41"/>
+    <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="C43:AK43"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
-    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="B72:AK72"/>
+    <mergeCell ref="A56:AK56"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B56:AK56"/>
-    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="B14:I19"/>
     <mergeCell ref="M24:P24"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="D68:AK68"/>
-    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="D59:AK59"/>
+    <mergeCell ref="C47:AK47"/>
     <mergeCell ref="D60:AK60"/>
-    <mergeCell ref="D69:AK69"/>
-    <mergeCell ref="C40:AK40"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="B76:AK76"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="B62:AK62"/>
+    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
